--- a/reports/Debug-purgatory-20260111/Month to Date (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260111/Month to Date (Prior Year)_Visits.xlsx
@@ -37,13 +37,13 @@
     <t>Purgatory Tickets</t>
   </si>
   <si>
-    <t>Purgatory Uplift Tickets</t>
-  </si>
-  <si>
     <t>Purgatory Coaster</t>
   </si>
   <si>
     <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
+    <t>Purgatory Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -605,10 +605,10 @@
         <v>45658</v>
       </c>
       <c r="C14" s="2">
-        <v>2335</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -619,7 +619,7 @@
         <v>45659</v>
       </c>
       <c r="C15" s="2">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -630,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C16" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -647,7 +647,7 @@
         <v>45660</v>
       </c>
       <c r="C17" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -661,10 +661,10 @@
         <v>45660</v>
       </c>
       <c r="C18" s="2">
-        <v>303</v>
+        <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C19" s="2">
-        <v>1656</v>
+        <v>1871</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>6</v>
@@ -686,10 +686,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C20" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,10 +700,10 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45662</v>
+        <v>45660</v>
       </c>
       <c r="C21" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -714,10 +714,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45663</v>
+        <v>45660</v>
       </c>
       <c r="C22" s="2">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45664</v>
+        <v>45661</v>
       </c>
       <c r="C23" s="2">
-        <v>1069</v>
+        <v>6</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,10 +742,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C24" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -770,10 +770,10 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45666</v>
+        <v>45663</v>
       </c>
       <c r="C26" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,10 +784,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C27" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -798,13 +798,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45667</v>
+        <v>45664</v>
       </c>
       <c r="C28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +812,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45668</v>
+        <v>45665</v>
       </c>
       <c r="C29" s="2">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C30" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -840,10 +840,10 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C31" s="2">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45658</v>
+        <v>45666</v>
       </c>
       <c r="C32" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45658</v>
+        <v>45667</v>
       </c>
       <c r="C33" s="2">
-        <v>380</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45658</v>
+        <v>45667</v>
       </c>
       <c r="C34" s="2">
-        <v>684</v>
+        <v>201</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45658</v>
+        <v>45668</v>
       </c>
       <c r="C35" s="2">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,10 +910,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C36" s="2">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,7 +924,7 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C37" s="2">
         <v>2</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C38" s="2">
-        <v>487</v>
+        <v>147</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,10 +952,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45662</v>
+        <v>45659</v>
       </c>
       <c r="C39" s="2">
-        <v>154</v>
+        <v>19</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45663</v>
+        <v>45660</v>
       </c>
       <c r="C40" s="2">
-        <v>1071</v>
+        <v>1733</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,10 +980,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45663</v>
+        <v>45661</v>
       </c>
       <c r="C41" s="2">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -994,10 +994,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45663</v>
+        <v>45661</v>
       </c>
       <c r="C42" s="2">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1008,13 +1008,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45664</v>
+        <v>45661</v>
       </c>
       <c r="C43" s="2">
-        <v>219</v>
+        <v>130</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,13 +1022,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45664</v>
+        <v>45662</v>
       </c>
       <c r="C44" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,13 +1036,13 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C45" s="2">
-        <v>1322</v>
+        <v>238</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,10 +1050,10 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45665</v>
+        <v>45663</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>899</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1064,13 +1064,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45666</v>
+        <v>45664</v>
       </c>
       <c r="C47" s="2">
-        <v>828</v>
+        <v>132</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C48" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1092,10 +1092,10 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C49" s="2">
-        <v>133</v>
+        <v>3</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C50" s="2">
+        <v>236</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C51" s="2">
-        <v>2250</v>
+        <v>4</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,10 +1134,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>45658</v>
+        <v>45667</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,10 +1148,10 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C53" s="2">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,10 +1162,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1179,10 +1179,10 @@
         <v>45660</v>
       </c>
       <c r="C55" s="2">
-        <v>1</v>
+        <v>672</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1193,10 +1193,10 @@
         <v>45660</v>
       </c>
       <c r="C56" s="2">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,13 +1204,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C57" s="2">
-        <v>1871</v>
+        <v>1965</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,7 +1218,7 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C58" s="2">
         <v>2</v>
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45660</v>
+        <v>45664</v>
       </c>
       <c r="C59" s="2">
-        <v>26</v>
+        <v>751</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45660</v>
+        <v>45664</v>
       </c>
       <c r="C60" s="2">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
@@ -1260,13 +1260,13 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45661</v>
+        <v>45666</v>
       </c>
       <c r="C61" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C62" s="2">
-        <v>6</v>
+        <v>1406</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1288,13 +1288,13 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C63" s="2">
-        <v>10</v>
+        <v>869</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,10 +1302,10 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>45663</v>
+        <v>45667</v>
       </c>
       <c r="C64" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>5</v>
@@ -1316,10 +1316,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45664</v>
+        <v>45667</v>
       </c>
       <c r="C65" s="2">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1330,13 +1330,13 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>45664</v>
+        <v>45658</v>
       </c>
       <c r="C66" s="2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45665</v>
+        <v>45658</v>
       </c>
       <c r="C67" s="2">
-        <v>167</v>
+        <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>5</v>
@@ -1358,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>45666</v>
+        <v>45659</v>
       </c>
       <c r="C68" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>5</v>
@@ -1372,13 +1372,13 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>45666</v>
+        <v>45659</v>
       </c>
       <c r="C69" s="2">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1386,13 +1386,13 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>45666</v>
+        <v>45659</v>
       </c>
       <c r="C70" s="2">
-        <v>7</v>
+        <v>2084</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1400,10 +1400,10 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>45667</v>
+        <v>45661</v>
       </c>
       <c r="C71" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>5</v>
@@ -1414,13 +1414,13 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>45667</v>
+        <v>45661</v>
       </c>
       <c r="C72" s="2">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1428,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>45668</v>
+        <v>45662</v>
       </c>
       <c r="C73" s="2">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>5</v>
@@ -1442,10 +1442,10 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>45658</v>
+        <v>45662</v>
       </c>
       <c r="C74" s="2">
-        <v>86</v>
+        <v>3</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>5</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>45659</v>
+        <v>45662</v>
       </c>
       <c r="C75" s="2">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1470,13 +1470,13 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
       <c r="C76" s="2">
-        <v>672</v>
+        <v>1125</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1484,13 +1484,13 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>45660</v>
+        <v>45664</v>
       </c>
       <c r="C77" s="2">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1498,10 +1498,10 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>45661</v>
+        <v>45664</v>
       </c>
       <c r="C78" s="2">
-        <v>1965</v>
+        <v>5</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>5</v>
@@ -1512,10 +1512,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>45662</v>
+        <v>45665</v>
       </c>
       <c r="C79" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1526,13 +1526,13 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="C80" s="2">
-        <v>751</v>
+        <v>995</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1540,10 +1540,10 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45664</v>
+        <v>45666</v>
       </c>
       <c r="C81" s="2">
-        <v>87</v>
+        <v>832</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>5</v>
@@ -1554,10 +1554,10 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="C82" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>5</v>
@@ -1571,7 +1571,7 @@
         <v>45667</v>
       </c>
       <c r="C83" s="2">
-        <v>1406</v>
+        <v>4</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>5</v>
@@ -1582,13 +1582,13 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="C84" s="2">
-        <v>869</v>
+        <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -1596,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="C85" s="2">
-        <v>4</v>
+        <v>988</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1610,10 +1610,10 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="C86" s="2">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>5</v>
@@ -1627,10 +1627,10 @@
         <v>45658</v>
       </c>
       <c r="C87" s="2">
-        <v>4</v>
+        <v>2335</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -1638,10 +1638,10 @@
         <v>1</v>
       </c>
       <c r="B88" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C88" s="2">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>5</v>
@@ -1652,13 +1652,13 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C89" s="2">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -1666,10 +1666,10 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C90" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>5</v>
@@ -1683,10 +1683,10 @@
         <v>45660</v>
       </c>
       <c r="C91" s="2">
-        <v>1733</v>
+        <v>303</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -1697,10 +1697,10 @@
         <v>45661</v>
       </c>
       <c r="C92" s="2">
-        <v>101</v>
+        <v>1656</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1708,10 +1708,10 @@
         <v>1</v>
       </c>
       <c r="B93" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C93" s="2">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>5</v>
@@ -1722,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="B94" s="2">
-        <v>45661</v>
+        <v>45662</v>
       </c>
       <c r="C94" s="2">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>5</v>
@@ -1736,10 +1736,10 @@
         <v>1</v>
       </c>
       <c r="B95" s="2">
-        <v>45662</v>
+        <v>45663</v>
       </c>
       <c r="C95" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>5</v>
@@ -1750,13 +1750,13 @@
         <v>1</v>
       </c>
       <c r="B96" s="2">
-        <v>45663</v>
+        <v>45664</v>
       </c>
       <c r="C96" s="2">
-        <v>238</v>
+        <v>1069</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1764,10 +1764,10 @@
         <v>1</v>
       </c>
       <c r="B97" s="2">
-        <v>45663</v>
+        <v>45665</v>
       </c>
       <c r="C97" s="2">
-        <v>899</v>
+        <v>4</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>5</v>
@@ -1778,10 +1778,10 @@
         <v>1</v>
       </c>
       <c r="B98" s="2">
-        <v>45664</v>
+        <v>45665</v>
       </c>
       <c r="C98" s="2">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>5</v>
@@ -1792,10 +1792,10 @@
         <v>1</v>
       </c>
       <c r="B99" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="C99" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="B100" s="2">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="C100" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>5</v>
@@ -1820,13 +1820,13 @@
         <v>1</v>
       </c>
       <c r="B101" s="2">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="C101" s="2">
-        <v>236</v>
+        <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1834,13 +1834,13 @@
         <v>1</v>
       </c>
       <c r="B102" s="2">
-        <v>45666</v>
+        <v>45668</v>
       </c>
       <c r="C102" s="2">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1848,10 +1848,10 @@
         <v>1</v>
       </c>
       <c r="B103" s="2">
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="C103" s="2">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>5</v>
@@ -1862,10 +1862,10 @@
         <v>1</v>
       </c>
       <c r="B104" s="2">
-        <v>45658</v>
+        <v>45668</v>
       </c>
       <c r="C104" s="2">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1879,7 +1879,7 @@
         <v>45658</v>
       </c>
       <c r="C105" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>5</v>
@@ -1890,13 +1890,13 @@
         <v>1</v>
       </c>
       <c r="B106" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C106" s="2">
-        <v>5</v>
+        <v>380</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1904,10 +1904,10 @@
         <v>1</v>
       </c>
       <c r="B107" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C107" s="2">
-        <v>311</v>
+        <v>684</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>8</v>
@@ -1918,13 +1918,13 @@
         <v>1</v>
       </c>
       <c r="B108" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C108" s="2">
-        <v>2084</v>
+        <v>21</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -1932,10 +1932,10 @@
         <v>1</v>
       </c>
       <c r="B109" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C109" s="2">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>5</v>
@@ -1946,10 +1946,10 @@
         <v>1</v>
       </c>
       <c r="B110" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C110" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>5</v>
@@ -1960,13 +1960,13 @@
         <v>1</v>
       </c>
       <c r="B111" s="2">
-        <v>45662</v>
+        <v>45661</v>
       </c>
       <c r="C111" s="2">
-        <v>1</v>
+        <v>487</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1977,7 +1977,7 @@
         <v>45662</v>
       </c>
       <c r="C112" s="2">
-        <v>3</v>
+        <v>154</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>5</v>
@@ -1988,13 +1988,13 @@
         <v>1</v>
       </c>
       <c r="B113" s="2">
-        <v>45662</v>
+        <v>45663</v>
       </c>
       <c r="C113" s="2">
-        <v>60</v>
+        <v>1071</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2002,13 +2002,13 @@
         <v>1</v>
       </c>
       <c r="B114" s="2">
-        <v>45662</v>
+        <v>45663</v>
       </c>
       <c r="C114" s="2">
-        <v>1125</v>
+        <v>3</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2016,10 +2016,10 @@
         <v>1</v>
       </c>
       <c r="B115" s="2">
-        <v>45664</v>
+        <v>45663</v>
       </c>
       <c r="C115" s="2">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>5</v>
@@ -2033,10 +2033,10 @@
         <v>45664</v>
       </c>
       <c r="C116" s="2">
-        <v>5</v>
+        <v>219</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2044,13 +2044,13 @@
         <v>1</v>
       </c>
       <c r="B117" s="2">
-        <v>45665</v>
+        <v>45664</v>
       </c>
       <c r="C117" s="2">
+        <v>4</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2061,10 +2061,10 @@
         <v>45665</v>
       </c>
       <c r="C118" s="2">
-        <v>995</v>
+        <v>1322</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2072,10 +2072,10 @@
         <v>1</v>
       </c>
       <c r="B119" s="2">
-        <v>45666</v>
+        <v>45665</v>
       </c>
       <c r="C119" s="2">
-        <v>832</v>
+        <v>1</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>5</v>
@@ -2086,13 +2086,13 @@
         <v>1</v>
       </c>
       <c r="B120" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C120" s="2">
-        <v>10</v>
+        <v>828</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2100,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="B121" s="2">
-        <v>45667</v>
+        <v>45666</v>
       </c>
       <c r="C121" s="2">
         <v>4</v>
@@ -2114,10 +2114,10 @@
         <v>1</v>
       </c>
       <c r="B122" s="2">
-        <v>45668</v>
+        <v>45666</v>
       </c>
       <c r="C122" s="2">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>5</v>
@@ -2128,13 +2128,13 @@
         <v>1</v>
       </c>
       <c r="B123" s="2">
-        <v>45668</v>
+        <v>45667</v>
       </c>
       <c r="C123" s="2">
-        <v>988</v>
+        <v>8</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2145,7 +2145,7 @@
         <v>45668</v>
       </c>
       <c r="C124" s="2">
-        <v>36</v>
+        <v>2250</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>5</v>
@@ -2176,7 +2176,7 @@
         <v>712</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2274,7 +2274,7 @@
         <v>288</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2358,7 +2358,7 @@
         <v>226</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2372,7 +2372,7 @@
         <v>17</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2428,7 +2428,7 @@
         <v>268</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4">
